--- a/data/google_news_dedup_audit_28_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_28_0426_UTC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7168147563934326</v>
+        <v>0.8433051109313965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -460,49 +460,133 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Verdachte van moordpoging in Merksplas gaat tolk te lijf tijdens verhoor: “Slachtoffer ernstig gewond” - HLN</t>
+          <t>Verdachte steekpartij in Merksplas slaat Roemeense tolk in gezicht, slachtoffer buiten levensgevaar - VRT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" t="n">
         <v>7</v>
       </c>
-      <c r="B3" t="n">
-        <v>9</v>
-      </c>
       <c r="C3" t="n">
-        <v>0.7201693058013916</v>
+        <v>0.7168146371841431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ex-voetbaltrainer uit Edegem veroordeeld tot 8 jaar cel en 5 jaar tbs voor zedenfeiten met minderjarigen - HLN</t>
+          <t>Slachtoffer steekpartij Merksplas is buiten levensgevaar, verdachte (22) slaat tolk tijdens verhoor - Nieuwsblad</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ex-voetbaltrainer uit Edegem kent straf na zedenfeiten met minderjarigen: “Hij nam jongens mee naar pretparken, daarna zocht hij toenadering” - HLN</t>
+          <t>Verdachte van moordpoging in Merksplas gaat tolk te lijf tijdens verhoor: “Slachtoffer ernstig gewond” - HLN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B4" t="n">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9710930585861206</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Raymond Asante scores in Patro’s playoff defeat to Beerschot - CediRates</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Raymond Asante scores in Patro’s playoff defeat to Beerschot - MyJoyOnline</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>22</v>
       </c>
-      <c r="C4" t="n">
+      <c r="B5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.7115242481231689</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Man taken to hospital after stabbing near busy road in Leytonstone - Guardian Series</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Man taken to hospital after stabbing near war memorial - London Now</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>41</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8313946723937988</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Marotta, incidente in autostrada: traffico bloccato, 4 km di coda - eTv Marche</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Marotta, incidente in autostrada poco dopo le 14: traffico bloccato, coda di 4 km. Si consiglia di uscire a Pesaro - Corriere Adriatico</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>41</v>
+      </c>
+      <c r="B7" t="n">
+        <v>44</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6860172748565674</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Marotta, incidente in autostrada: traffico bloccato, 4 km di coda - eTv Marche</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Incidente A14 oggi: tratto riaperto ma 4 km di coda tra Pesaro e Marotta - SICURAUTO.it</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>41</v>
+      </c>
+      <c r="B8" t="n">
+        <v>45</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8404203653335571</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Marotta, incidente in autostrada: traffico bloccato, 4 km di coda - eTv Marche</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Marotta, incidente in autostrada poco dopo le 14: traffico bloccato, coda di 3 km - Corriere Adriatico</t>
         </is>
       </c>
     </row>
